--- a/input/Contractor.xlsx
+++ b/input/Contractor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8297F72-1E10-42A9-A5B2-E382E4F583DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EF3C15-3368-4F73-8894-49CFFC208631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="CEWithoutAadhar" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Mobile Number</t>
   </si>
@@ -52,23 +51,35 @@
     <t>DOB</t>
   </si>
   <si>
-    <t>Karishma</t>
-  </si>
-  <si>
-    <t>10-08-2025</t>
+    <t>8/10/2025</t>
+  </si>
+  <si>
+    <t>Jithu</t>
+  </si>
+  <si>
+    <t>939544304342</t>
+  </si>
+  <si>
+    <t>6385573882</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF5C92FF"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -91,9 +102,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -430,13 +444,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F873A05F-98AA-4B8C-BC99-F5F8F22A7373}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,8 +458,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -455,26 +474,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8B4F16-01C9-4CE9-B81D-F62201D04EEB}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/input/Contractor.xlsx
+++ b/input/Contractor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EF3C15-3368-4F73-8894-49CFFC208631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A41A413-F7F9-458B-9879-B05BC41EDA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <t>939544304342</t>
   </si>
   <si>
-    <t>6385573882</t>
+    <t>6381084434</t>
   </si>
 </sst>
 </file>

--- a/input/Contractor.xlsx
+++ b/input/Contractor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A41A413-F7F9-458B-9879-B05BC41EDA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35ECB3A-8FD6-4ABA-8870-EE4F7C706A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
@@ -57,10 +57,10 @@
     <t>Jithu</t>
   </si>
   <si>
-    <t>939544304342</t>
-  </si>
-  <si>
-    <t>6381084434</t>
+    <t>7339406338</t>
+  </si>
+  <si>
+    <t>656658843615</t>
   </si>
 </sst>
 </file>
@@ -460,10 +460,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/input/Contractor.xlsx
+++ b/input/Contractor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35ECB3A-8FD6-4ABA-8870-EE4F7C706A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9BBAA2-15BA-4E3E-B288-E8AA646697C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="15375" windowHeight="7785" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
   <sheets>
     <sheet name="CEWithAadhar" sheetId="1" r:id="rId1"/>
